--- a/DateBase/orders/Nha Thu_2026-8-10.xlsx
+++ b/DateBase/orders/Nha Thu_2026-8-10.xlsx
@@ -689,6 +689,9 @@
       <c r="C31" t="str">
         <v>788_国产直葱白_undefined_undefined_1bunch</v>
       </c>
+      <c r="F31" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -747,7 +750,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01410510106112858710101021710101010101070510105100</v>
+        <v>014105101061128587101010217101010101010705101051010</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-8-10.xlsx
+++ b/DateBase/orders/Nha Thu_2026-8-10.xlsx
@@ -752,6 +752,9 @@
       <c r="G2" t="str">
         <v>014105101061128587101010217101010101010705101051010</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
